--- a/data/trans_orig/P33B3_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P33B3_2023-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Poblacion según la frecuencia con la que se despierta demasiado temprano de forma involuntaria en 2023</t>
+          <t>Poblacion según la frecuencia con la que se despierta demasiado temprano de forma involuntaria en 2023 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>67767</t>
+          <t>67118</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>97763</t>
+          <t>98070</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>143128</t>
+          <t>143752</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>178045</t>
+          <t>181162</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>221025</t>
+          <t>218810</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>268351</t>
+          <t>265076</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>20,9%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>47963</t>
+          <t>47100</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>71626</t>
+          <t>72321</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>110348</t>
+          <t>109972</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>139053</t>
+          <t>139813</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>164698</t>
+          <t>164316</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>202750</t>
+          <t>202093</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,94%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>66944</t>
+          <t>65507</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>98357</t>
+          <t>96314</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>150667</t>
+          <t>149432</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>182470</t>
+          <t>182505</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>223974</t>
+          <t>226673</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>270668</t>
+          <t>270035</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,29%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>272158</t>
+          <t>274108</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>314034</t>
+          <t>313207</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>52,85%</t>
+          <t>53,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>60,98%</t>
+          <t>60,82%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>281922</t>
+          <t>282269</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>323755</t>
+          <t>324889</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>37,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>42,99%</t>
+          <t>43,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>566158</t>
+          <t>569255</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>628119</t>
+          <t>625641</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>44,65%</t>
+          <t>44,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>49,53%</t>
+          <t>49,34%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>106172</t>
+          <t>99637</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>180438</t>
+          <t>178330</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>111950</t>
+          <t>115012</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>181421</t>
+          <t>179704</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>233681</t>
+          <t>241115</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>346484</t>
+          <t>348208</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,69%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>88578</t>
+          <t>90052</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>161442</t>
+          <t>162246</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>144636</t>
+          <t>146387</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>234130</t>
+          <t>233567</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>259360</t>
+          <t>266790</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>379260</t>
+          <t>378415</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,36%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>242377</t>
+          <t>237430</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>388420</t>
+          <t>390939</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>284290</t>
+          <t>285023</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>444293</t>
+          <t>444613</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>560179</t>
+          <t>594712</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>807813</t>
+          <t>813097</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,96%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1584705</t>
+          <t>1582789</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1840049</t>
+          <t>1868167</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>69,22%</t>
+          <t>69,14%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>80,38%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1395529</t>
+          <t>1396288</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1693479</t>
+          <t>1685034</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>62,36%</t>
+          <t>62,39%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>75,68%</t>
+          <t>75,3%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3026778</t>
+          <t>3021915</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3475457</t>
+          <t>3431214</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>66,86%</t>
+          <t>66,75%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>76,77%</t>
+          <t>75,79%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>27199</t>
+          <t>27463</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>53126</t>
+          <t>54196</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>30613</t>
+          <t>31695</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>53126</t>
+          <t>51853</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>63466</t>
+          <t>64074</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>96056</t>
+          <t>98632</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,55%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>30844</t>
+          <t>32109</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>59103</t>
+          <t>60573</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>43762</t>
+          <t>44354</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>68456</t>
+          <t>68039</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>81682</t>
+          <t>80706</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>118824</t>
+          <t>117837</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,02%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>101128</t>
+          <t>99603</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>140183</t>
+          <t>139336</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>126639</t>
+          <t>127554</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>161640</t>
+          <t>162271</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>238457</t>
+          <t>238106</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>289692</t>
+          <t>291423</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>22,31%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>418681</t>
+          <t>418729</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>468312</t>
+          <t>468422</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>72,53%</t>
+          <t>72,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>400869</t>
+          <t>400677</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>442185</t>
+          <t>444473</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>60,7%</t>
+          <t>60,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>66,95%</t>
+          <t>67,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>832323</t>
+          <t>833841</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>897959</t>
+          <t>899949</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>63,72%</t>
+          <t>63,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>68,75%</t>
+          <t>68,9%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>204476</t>
+          <t>197960</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>306112</t>
+          <t>301871</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>291908</t>
+          <t>282228</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>394475</t>
+          <t>392935</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>537611</t>
+          <t>538349</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>683330</t>
+          <t>677959</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,55%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>182057</t>
+          <t>185136</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>271388</t>
+          <t>270067</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>300605</t>
+          <t>310249</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>420302</t>
+          <t>419715</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>536090</t>
+          <t>536691</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>674993</t>
+          <t>672756</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,47%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>412347</t>
+          <t>417015</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>592647</t>
+          <t>595542</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>573085</t>
+          <t>558693</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>766017</t>
+          <t>759845</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1068806</t>
+          <t>1076599</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1331573</t>
+          <t>1328750</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,71%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2317507</t>
+          <t>2314104</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2657123</t>
+          <t>2646430</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>67,18%</t>
+          <t>67,08%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>77,02%</t>
+          <t>76,71%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2102019</t>
+          <t>2104722</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2494950</t>
+          <t>2481162</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>57,57%</t>
+          <t>57,64%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>68,33%</t>
+          <t>67,95%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4456944</t>
+          <t>4459599</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4963864</t>
+          <t>4935875</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>62,76%</t>
+          <t>62,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>69,51%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P33B3_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P33B3_2023-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>80941</t>
+          <t>87425</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>67118</t>
+          <t>72893</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>98070</t>
+          <t>103374</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>160572</t>
+          <t>176517</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>143752</t>
+          <t>160086</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>181162</t>
+          <t>196333</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>241513</t>
+          <t>263942</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>218810</t>
+          <t>240866</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>265076</t>
+          <t>286175</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,44%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>58807</t>
+          <t>61888</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>47100</t>
+          <t>49634</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>72321</t>
+          <t>75703</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>123858</t>
+          <t>135689</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>109972</t>
+          <t>120103</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>139813</t>
+          <t>151994</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>182665</t>
+          <t>197577</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>164316</t>
+          <t>177847</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>202093</t>
+          <t>219515</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>15,68%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>80502</t>
+          <t>86414</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>65507</t>
+          <t>71614</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>96314</t>
+          <t>102782</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>165876</t>
+          <t>179361</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>149432</t>
+          <t>162277</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>182505</t>
+          <t>197282</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>246378</t>
+          <t>265776</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>226673</t>
+          <t>243445</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>270035</t>
+          <t>291603</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>20,83%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>294689</t>
+          <t>342802</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>274108</t>
+          <t>319165</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>313207</t>
+          <t>364740</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>57,23%</t>
+          <t>59,25%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>53,23%</t>
+          <t>55,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>60,82%</t>
+          <t>63,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>302861</t>
+          <t>329747</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>282269</t>
+          <t>309577</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>324889</t>
+          <t>351853</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>40,21%</t>
+          <t>40,15%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>43,14%</t>
+          <t>42,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>597551</t>
+          <t>672550</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>569255</t>
+          <t>636860</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>625641</t>
+          <t>705042</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>47,12%</t>
+          <t>48,04%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>45,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>49,34%</t>
+          <t>50,37%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>753168</t>
+          <t>821315</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>753168</t>
+          <t>821315</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>753168</t>
+          <t>821315</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1268107</t>
+          <t>1399845</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1268107</t>
+          <t>1399845</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1268107</t>
+          <t>1399845</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>146085</t>
+          <t>161217</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>99637</t>
+          <t>139708</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>178330</t>
+          <t>191480</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>152640</t>
+          <t>175332</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>115012</t>
+          <t>155356</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>179704</t>
+          <t>198234</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>298726</t>
+          <t>336549</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>241115</t>
+          <t>303955</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>348208</t>
+          <t>370592</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>8,42%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>132385</t>
+          <t>141326</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>90052</t>
+          <t>120219</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>162246</t>
+          <t>167324</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>200640</t>
+          <t>223108</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>146387</t>
+          <t>200305</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>233567</t>
+          <t>251006</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>333025</t>
+          <t>364434</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>266790</t>
+          <t>331646</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>378415</t>
+          <t>403591</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>9,17%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>333733</t>
+          <t>363831</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>237430</t>
+          <t>330478</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>390939</t>
+          <t>402841</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>388486</t>
+          <t>429517</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>285023</t>
+          <t>399424</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>444613</t>
+          <t>465788</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>722220</t>
+          <t>793348</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>594712</t>
+          <t>745627</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>813097</t>
+          <t>848075</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>19,27%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1677093</t>
+          <t>1563111</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1582789</t>
+          <t>1513616</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1868167</t>
+          <t>1606942</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>73,26%</t>
+          <t>70,11%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>69,14%</t>
+          <t>67,89%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>81,6%</t>
+          <t>72,08%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1496056</t>
+          <t>1343436</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1396288</t>
+          <t>1302322</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1685034</t>
+          <t>1383425</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>66,85%</t>
+          <t>61,87%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>62,39%</t>
+          <t>59,98%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>75,3%</t>
+          <t>63,71%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>3173150</t>
+          <t>2906546</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3021915</t>
+          <t>2838442</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3431214</t>
+          <t>2968166</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>70,09%</t>
+          <t>66,04%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>66,75%</t>
+          <t>64,5%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>75,79%</t>
+          <t>67,44%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2289297</t>
+          <t>2229485</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2289297</t>
+          <t>2229485</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2289297</t>
+          <t>2229485</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>4527121</t>
+          <t>4400877</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4527121</t>
+          <t>4400877</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4527121</t>
+          <t>4400877</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>38946</t>
+          <t>43710</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>27463</t>
+          <t>30850</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>54196</t>
+          <t>59796</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>40333</t>
+          <t>47511</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>31695</t>
+          <t>37200</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>51853</t>
+          <t>59863</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>79279</t>
+          <t>91221</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>64074</t>
+          <t>74407</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>98632</t>
+          <t>109930</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,61%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>43004</t>
+          <t>49009</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>32109</t>
+          <t>36333</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>60573</t>
+          <t>69421</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>54512</t>
+          <t>61507</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>44354</t>
+          <t>49705</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>68039</t>
+          <t>75518</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>97516</t>
+          <t>110517</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>80706</t>
+          <t>91056</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>117837</t>
+          <t>134570</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,31%</t>
         </is>
       </c>
     </row>
@@ -2089,67 +2089,67 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>119015</t>
+          <t>135043</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>99603</t>
+          <t>116272</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>139336</t>
+          <t>155896</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
+          <t>21,94%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>158563</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>140223</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>178488</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
           <t>21,58%</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>252</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>143562</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>127554</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>162271</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>21,74%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>262577</t>
+          <t>293606</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>238106</t>
+          <t>267134</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>291423</t>
+          <t>323044</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,35%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>444688</t>
+          <t>482837</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>418729</t>
+          <t>454749</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>468422</t>
+          <t>509143</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>68,87%</t>
+          <t>67,95%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>64,85%</t>
+          <t>64,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>72,55%</t>
+          <t>71,65%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>422056</t>
+          <t>467295</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>400677</t>
+          <t>443806</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>444473</t>
+          <t>488550</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>63,9%</t>
+          <t>63,59%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>60,67%</t>
+          <t>60,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>67,3%</t>
+          <t>66,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>866745</t>
+          <t>950132</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>833841</t>
+          <t>913645</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>899949</t>
+          <t>983121</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>66,36%</t>
+          <t>65,73%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>63,84%</t>
+          <t>63,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>68,9%</t>
+          <t>68,01%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>645654</t>
+          <t>710599</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>645654</t>
+          <t>710599</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>645654</t>
+          <t>710599</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1306117</t>
+          <t>1445477</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1306117</t>
+          <t>1445477</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1306117</t>
+          <t>1445477</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>265973</t>
+          <t>292352</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>197960</t>
+          <t>261312</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>301871</t>
+          <t>332612</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>353545</t>
+          <t>399360</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>282228</t>
+          <t>367005</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>392935</t>
+          <t>431459</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>619518</t>
+          <t>691712</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>538349</t>
+          <t>647611</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>677959</t>
+          <t>733476</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>10,12%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>234196</t>
+          <t>252223</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>185136</t>
+          <t>223676</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>270067</t>
+          <t>287149</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>379010</t>
+          <t>420305</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>310249</t>
+          <t>387492</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>419715</t>
+          <t>455190</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>613206</t>
+          <t>672528</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>536691</t>
+          <t>628878</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>672756</t>
+          <t>719392</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,93%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>533250</t>
+          <t>585288</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>417015</t>
+          <t>541032</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>595542</t>
+          <t>635877</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>697925</t>
+          <t>767442</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>558693</t>
+          <t>726127</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>759845</t>
+          <t>808754</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1231175</t>
+          <t>1352730</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1076599</t>
+          <t>1288542</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1328750</t>
+          <t>1414017</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>19,51%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>2416471</t>
+          <t>2388750</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2314104</t>
+          <t>2324534</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2646430</t>
+          <t>2449079</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>70,04%</t>
+          <t>67,89%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>67,08%</t>
+          <t>66,06%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>76,71%</t>
+          <t>69,6%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2220975</t>
+          <t>2140478</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2104722</t>
+          <t>2086654</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2481162</t>
+          <t>2191181</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>60,82%</t>
+          <t>57,42%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>57,64%</t>
+          <t>55,98%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>67,95%</t>
+          <t>58,78%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>4637445</t>
+          <t>4529228</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4459599</t>
+          <t>4444726</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4935875</t>
+          <t>4607039</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>65,3%</t>
+          <t>62,5%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>62,8%</t>
+          <t>61,34%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>69,51%</t>
+          <t>63,58%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3449890</t>
+          <t>3518613</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3449890</t>
+          <t>3518613</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3449890</t>
+          <t>3518613</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3651455</t>
+          <t>3727585</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3651455</t>
+          <t>3727585</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3651455</t>
+          <t>3727585</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>7101345</t>
+          <t>7246198</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>7101345</t>
+          <t>7246198</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7101345</t>
+          <t>7246198</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
